--- a/data/trans_orig/IP42E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP42E-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86318</t>
+          <t>86196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100993</t>
+          <t>100940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85136</t>
+          <t>85085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101774</t>
+          <t>101230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175297</t>
+          <t>176576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>197751</t>
+          <t>197854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22091</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27064</t>
+          <t>26931</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26196</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44126</t>
+          <t>43390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106290</t>
+          <t>105406</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123406</t>
+          <t>124027</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125078</t>
+          <t>123401</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142623</t>
+          <t>142434</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236287</t>
+          <t>234958</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>260504</t>
+          <t>261074</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11839</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25743</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12829</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23779</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>31823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32688</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51542</t>
+          <t>50528</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77066</t>
+          <t>77029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90916</t>
+          <t>90769</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84384</t>
+          <t>84006</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99434</t>
+          <t>99276</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>166370</t>
+          <t>166236</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>187126</t>
+          <t>187060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>17785</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21028</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15691</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15774</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>26149</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115939</t>
+          <t>115981</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>134389</t>
+          <t>135284</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>120195</t>
+          <t>120098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>136454</t>
+          <t>136232</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>241242</t>
+          <t>240416</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>266316</t>
+          <t>265137</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -3683,82 +3683,82 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>5946</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
           <t>709</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>5877</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2205</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18339</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13137</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>26735</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20156</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>23823</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>41778</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>403201</t>
+          <t>403273</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>434977</t>
+          <t>434901</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>430633</t>
+          <t>432587</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>463716</t>
+          <t>466291</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>843521</t>
+          <t>844000</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>888914</t>
+          <t>889716</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34371</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>35685</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>58731</t>
+          <t>56820</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -4591,12 +4591,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23889</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>41257</t>
+          <t>41278</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>45562</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>69529</t>
+          <t>70344</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4945,82 +4945,82 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>10784</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>6450</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>17172</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>24311</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>17322</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>33660</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>10784</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>6630</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>17699</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>24311</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>17628</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>33225</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>47489</t>
+          <t>47640</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>71422</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>55938</t>
+          <t>54676</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>80261</t>
+          <t>80227</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>109554</t>
+          <t>111321</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>145346</t>
+          <t>145206</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86106</t>
+          <t>86859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102041</t>
+          <t>101688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85735</t>
+          <t>86193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102775</t>
+          <t>102936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176631</t>
+          <t>178080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199590</t>
+          <t>200652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>29717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>27997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47108</t>
+          <t>47754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115326</t>
+          <t>115675</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>133934</t>
+          <t>133292</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135603</t>
+          <t>135083</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154351</t>
+          <t>154394</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257624</t>
+          <t>257097</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>283872</t>
+          <t>284041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24009</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20646</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28694</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7063,12 +7063,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -7091,12 +7091,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19590</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34559</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33062</t>
+          <t>32810</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>53416</t>
+          <t>52965</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -7321,12 +7321,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89870</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103093</t>
+          <t>102997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89473</t>
+          <t>89300</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105503</t>
+          <t>105239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>184283</t>
+          <t>183841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>205172</t>
+          <t>205149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7484,12 +7484,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7519,12 +7519,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -7582,12 +7582,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7632,12 +7632,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -7695,12 +7695,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -7999,12 +7999,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15394</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>21375</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33042</t>
+          <t>31745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -8229,12 +8229,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115045</t>
+          <t>115153</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>134056</t>
+          <t>134706</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>112667</t>
+          <t>111545</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>130860</t>
+          <t>130813</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>231989</t>
+          <t>233330</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>259204</t>
+          <t>259141</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,11%</t>
         </is>
       </c>
     </row>
@@ -8342,12 +8342,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8357,12 +8357,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>17051</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>32135</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>114</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8681,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -8794,12 +8794,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -8907,12 +8907,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>26094</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27302</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8977,12 +8977,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>27894</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48586</t>
+          <t>46700</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>425042</t>
+          <t>424532</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>459450</t>
+          <t>458409</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>441398</t>
+          <t>443122</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>477129</t>
+          <t>478962</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>875951</t>
+          <t>876259</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>925852</t>
+          <t>925533</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -9250,12 +9250,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>36956</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>40156</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>46905</t>
+          <t>45937</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>73182</t>
+          <t>70215</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -9363,12 +9363,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9511,12 +9511,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>30550</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>43868</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>67027</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9772,12 +9772,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>57906</t>
+          <t>56052</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>83092</t>
+          <t>82234</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>59339</t>
+          <t>58109</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>84966</t>
+          <t>84994</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>123732</t>
+          <t>121760</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>161800</t>
+          <t>157282</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -10277,12 +10277,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81706</t>
+          <t>81838</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93532</t>
+          <t>93299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85990</t>
+          <t>86967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100921</t>
+          <t>100995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10347,12 +10347,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>173027</t>
+          <t>173263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191325</t>
+          <t>190807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10729,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -10955,12 +10955,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10990,12 +10990,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19581</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>14140</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>29627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123103</t>
+          <t>122993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137955</t>
+          <t>137461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11220,12 +11220,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141225</t>
+          <t>141189</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155324</t>
+          <t>154966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11255,12 +11255,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>268924</t>
+          <t>269745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>289107</t>
+          <t>289236</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -11863,12 +11863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25229</t>
+          <t>24817</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11878,12 +11878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11913,12 +11913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22551</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11948,12 +11948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95355</t>
+          <t>94757</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106591</t>
+          <t>107095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86728</t>
+          <t>86490</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98405</t>
+          <t>99199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>186002</t>
+          <t>185902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>202529</t>
+          <t>202108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -12206,12 +12206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12221,12 +12221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12786,12 +12786,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12806,12 +12806,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26180</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -13001,12 +13001,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>108696</t>
+          <t>108035</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>126068</t>
+          <t>126185</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13016,12 +13016,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106734</t>
+          <t>104631</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>122410</t>
+          <t>122724</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>219634</t>
+          <t>220249</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>244231</t>
+          <t>243832</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -13114,12 +13114,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13129,12 +13129,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13164,12 +13164,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -13227,12 +13227,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13262,12 +13262,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13277,12 +13277,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13297,12 +13297,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13312,12 +13312,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -13453,12 +13453,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13468,12 +13468,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15329</t>
+          <t>15912</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -13571,7 +13571,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -13636,12 +13636,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13651,12 +13651,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -13679,12 +13679,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13694,12 +13694,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13714,12 +13714,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13729,12 +13729,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13749,12 +13749,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>24648</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>42994</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13764,12 +13764,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -13909,12 +13909,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>424946</t>
+          <t>424933</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>451894</t>
+          <t>453920</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13924,12 +13924,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>436857</t>
+          <t>436492</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>465309</t>
+          <t>465351</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>871915</t>
+          <t>870386</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>909984</t>
+          <t>909948</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -14022,12 +14022,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14037,12 +14037,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14057,12 +14057,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>27208</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14072,12 +14072,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14092,12 +14092,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>22969</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>40826</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14107,12 +14107,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14205,12 +14205,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14283,12 +14283,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>523</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -14361,12 +14361,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14396,12 +14396,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14411,12 +14411,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>33214</t>
+          <t>33527</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -14474,12 +14474,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14509,12 +14509,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14544,12 +14544,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -14587,12 +14587,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>42998</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>65381</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>38598</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>59829</t>
+          <t>60345</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14637,12 +14637,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>86954</t>
+          <t>85453</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>118900</t>
+          <t>117847</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14672,12 +14672,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -18751,12 +18751,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -18766,12 +18766,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -19138,7 +19138,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19153,7 +19153,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -19399,7 +19399,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19449,7 +19449,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
